--- a/results/optA_20251016_200330/experiments/experiment_iml_lifecycle/table9_classification_pivot.xlsx
+++ b/results/optA_20251016_200330/experiments/experiment_iml_lifecycle/table9_classification_pivot.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8652</v>
+        <v>0.8962</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8764</v>
+        <v>0.9151</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8315</v>
+        <v>0.9151</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8427</v>
+        <v>0.9151</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8315</v>
+        <v>0.8585</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8774</v>
       </c>
     </row>
     <row r="3">
@@ -529,22 +529,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8153</v>
+        <v>0.8875</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.9035</v>
       </c>
       <c r="E3" t="n">
-        <v>0.711</v>
+        <v>0.9196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7177</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7055</v>
+        <v>0.8786</v>
       </c>
     </row>
     <row r="4">
@@ -559,22 +559,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9302</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9091</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.907</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8837</v>
+        <v>0.9583</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8864</v>
+        <v>0.9375</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9024</v>
+        <v>0.9574</v>
       </c>
     </row>
     <row r="5">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9756</v>
+        <v>0.9184</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9756</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9512</v>
+        <v>0.9184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9268</v>
+        <v>0.9388</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9512</v>
+        <v>0.9184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9024</v>
+        <v>0.9184</v>
       </c>
     </row>
     <row r="6">
@@ -611,22 +611,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9524</v>
+        <v>0.9474</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9412</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9286</v>
+        <v>0.9474</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9048</v>
+        <v>0.9485</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9176</v>
+        <v>0.9278</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9024</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="7">
@@ -637,22 +637,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>0.8293</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.9167</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.9231</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.8621</v>
+        <v>0.8919</v>
       </c>
       <c r="F8" t="n">
-        <v>0.96</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8571</v>
+        <v>0.8611</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8571</v>
+        <v>0.9394</v>
       </c>
     </row>
     <row r="9">
@@ -693,22 +693,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7857</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8571</v>
+        <v>0.9706</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8929</v>
+        <v>0.9706</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8571</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8571</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8571</v>
+        <v>0.9118000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -719,22 +719,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8462</v>
+        <v>0.9067</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8889</v>
+        <v>0.9429</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8772</v>
+        <v>0.9296</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9444</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8571</v>
+        <v>0.8857</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8571</v>
+        <v>0.9254</v>
       </c>
     </row>
     <row r="11">
@@ -745,22 +745,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -775,22 +775,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.6667</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.75</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -827,22 +827,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5714</v>
+        <v>0.8889</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4444</v>
+        <v>0.8889</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5714</v>
+        <v>0.75</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4444</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -883,22 +883,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7059</v>
+        <v>0.8</v>
       </c>
       <c r="D16" t="n">
-        <v>0.75</v>
+        <v>0.8125</v>
       </c>
       <c r="E16" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.6667</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.6471</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.6429</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="17">
@@ -909,22 +909,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.75</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>0.6842</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5</v>
+        <v>0.7895</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6875</v>
+        <v>0.6842</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5625</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5625</v>
+        <v>0.6842</v>
       </c>
     </row>
     <row r="18">
@@ -935,22 +935,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7059</v>
       </c>
       <c r="D18" t="n">
-        <v>0.75</v>
+        <v>0.7429</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5714</v>
+        <v>0.8108</v>
       </c>
       <c r="F18" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6486</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.6667</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5806</v>
       </c>
     </row>
     <row r="19">
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
